--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-09-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBDB195-1325-4BAD-AA93-711E93A2B2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3A3524-B509-48DF-B880-048735163F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11880" yWindow="1620" windowWidth="14880" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9075" yWindow="2085" windowWidth="14880" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="385">
   <si>
     <t>SKU</t>
   </si>
@@ -1112,6 +1112,69 @@
   </si>
   <si>
     <t>£2756.16</t>
+  </si>
+  <si>
+    <t>£17.50</t>
+  </si>
+  <si>
+    <t>£21.25</t>
+  </si>
+  <si>
+    <t>£22.50</t>
+  </si>
+  <si>
+    <t>£28.50</t>
+  </si>
+  <si>
+    <t>£32.00</t>
+  </si>
+  <si>
+    <t>£30.00</t>
+  </si>
+  <si>
+    <t>£35.50</t>
+  </si>
+  <si>
+    <t>£38.50</t>
+  </si>
+  <si>
+    <t>£48.00</t>
+  </si>
+  <si>
+    <t>£49.00</t>
+  </si>
+  <si>
+    <t>£58.00</t>
+  </si>
+  <si>
+    <t>£995.00</t>
+  </si>
+  <si>
+    <t>£46.52</t>
+  </si>
+  <si>
+    <t>£54.66</t>
+  </si>
+  <si>
+    <t>£57.94</t>
+  </si>
+  <si>
+    <t>£64.66</t>
+  </si>
+  <si>
+    <t>£69.00</t>
+  </si>
+  <si>
+    <t>£65.00</t>
+  </si>
+  <si>
+    <t>£1750.00</t>
+  </si>
+  <si>
+    <t>£1900.00</t>
+  </si>
+  <si>
+    <t>£1850.00</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1618,7 @@
         <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
         <v>103</v>
@@ -1611,7 +1674,7 @@
         <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="G3" t="s">
         <v>104</v>
@@ -1667,7 +1730,7 @@
         <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>365</v>
       </c>
       <c r="G4" t="s">
         <v>105</v>
@@ -1723,7 +1786,7 @@
         <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>106</v>
+        <v>366</v>
       </c>
       <c r="G5" t="s">
         <v>106</v>
@@ -1779,7 +1842,7 @@
         <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>367</v>
       </c>
       <c r="G6" t="s">
         <v>107</v>
@@ -1835,7 +1898,7 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>108</v>
+        <v>368</v>
       </c>
       <c r="G7" t="s">
         <v>108</v>
@@ -1891,7 +1954,7 @@
         <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>109</v>
+        <v>369</v>
       </c>
       <c r="G8" t="s">
         <v>109</v>
@@ -1947,7 +2010,7 @@
         <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>110</v>
+        <v>370</v>
       </c>
       <c r="G9" t="s">
         <v>110</v>
@@ -2003,7 +2066,7 @@
         <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>111</v>
+        <v>371</v>
       </c>
       <c r="G10" t="s">
         <v>111</v>
@@ -2059,7 +2122,7 @@
         <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>112</v>
+        <v>371</v>
       </c>
       <c r="G11" t="s">
         <v>112</v>
@@ -2115,7 +2178,7 @@
         <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>372</v>
       </c>
       <c r="G12" t="s">
         <v>113</v>
@@ -2171,7 +2234,7 @@
         <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>114</v>
+        <v>373</v>
       </c>
       <c r="G13" t="s">
         <v>114</v>
@@ -2227,7 +2290,7 @@
         <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>374</v>
       </c>
       <c r="G14" t="s">
         <v>115</v>
@@ -2283,7 +2346,7 @@
         <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>116</v>
+        <v>228</v>
       </c>
       <c r="G15" t="s">
         <v>116</v>
@@ -2339,7 +2402,7 @@
         <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="G16" t="s">
         <v>117</v>
@@ -2395,7 +2458,7 @@
         <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>375</v>
       </c>
       <c r="G17" t="s">
         <v>101</v>
@@ -2451,7 +2514,7 @@
         <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s">
         <v>118</v>
@@ -2507,7 +2570,7 @@
         <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>119</v>
+        <v>376</v>
       </c>
       <c r="G19" t="s">
         <v>119</v>
@@ -2563,7 +2626,7 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>377</v>
       </c>
       <c r="G20" t="s">
         <v>91</v>
@@ -2619,7 +2682,7 @@
         <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
+        <v>378</v>
       </c>
       <c r="G21" t="s">
         <v>120</v>
@@ -2675,7 +2738,7 @@
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>379</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -2731,7 +2794,7 @@
         <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>380</v>
       </c>
       <c r="G23" t="s">
         <v>101</v>
@@ -2787,7 +2850,7 @@
         <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>101</v>
+        <v>380</v>
       </c>
       <c r="G24" t="s">
         <v>101</v>
@@ -2899,7 +2962,7 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>101</v>
+        <v>381</v>
       </c>
       <c r="G26" t="s">
         <v>101</v>
@@ -2955,7 +3018,7 @@
         <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>382</v>
       </c>
       <c r="G27" t="s">
         <v>101</v>
@@ -3011,7 +3074,7 @@
         <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>101</v>
+        <v>383</v>
       </c>
       <c r="G28" t="s">
         <v>101</v>
@@ -3067,7 +3130,7 @@
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>101</v>
+        <v>384</v>
       </c>
       <c r="G29" t="s">
         <v>101</v>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-09-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3A3524-B509-48DF-B880-048735163F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFC9EFA-FF80-49E6-AA96-8F0D252F6B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9075" yWindow="2085" windowWidth="14880" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="3150" windowWidth="14880" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1027,9 +1027,6 @@
     <t>£14.33</t>
   </si>
   <si>
-    <t>£16.82</t>
-  </si>
-  <si>
     <t>£21.37</t>
   </si>
   <si>
@@ -1078,21 +1075,12 @@
     <t>£41.49</t>
   </si>
   <si>
-    <t>£49.57</t>
-  </si>
-  <si>
-    <t>£53.22</t>
-  </si>
-  <si>
     <t>£59.29</t>
   </si>
   <si>
     <t>£68.51</t>
   </si>
   <si>
-    <t>£62.42</t>
-  </si>
-  <si>
     <t>£62.06</t>
   </si>
   <si>
@@ -1175,6 +1163,18 @@
   </si>
   <si>
     <t>£1850.00</t>
+  </si>
+  <si>
+    <t>£16.73</t>
+  </si>
+  <si>
+    <t>£49.15</t>
+  </si>
+  <si>
+    <t>£53.12</t>
+  </si>
+  <si>
+    <t>£61.80</t>
   </si>
 </sst>
 </file>
@@ -1674,7 +1674,7 @@
         <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G3" t="s">
         <v>104</v>
@@ -1707,7 +1707,7 @@
         <v>287</v>
       </c>
       <c r="Q3" t="s">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="R3" t="s">
         <v>302</v>
@@ -1730,7 +1730,7 @@
         <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="G4" t="s">
         <v>105</v>
@@ -1763,7 +1763,7 @@
         <v>76</v>
       </c>
       <c r="Q4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="R4" t="s">
         <v>303</v>
@@ -1786,7 +1786,7 @@
         <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G5" t="s">
         <v>106</v>
@@ -1819,7 +1819,7 @@
         <v>288</v>
       </c>
       <c r="Q5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R5" t="s">
         <v>304</v>
@@ -1842,7 +1842,7 @@
         <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G6" t="s">
         <v>107</v>
@@ -1875,7 +1875,7 @@
         <v>289</v>
       </c>
       <c r="Q6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R6" t="s">
         <v>305</v>
@@ -1898,7 +1898,7 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G7" t="s">
         <v>108</v>
@@ -1931,7 +1931,7 @@
         <v>79</v>
       </c>
       <c r="Q7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R7" t="s">
         <v>306</v>
@@ -1954,7 +1954,7 @@
         <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G8" t="s">
         <v>109</v>
@@ -1987,7 +1987,7 @@
         <v>80</v>
       </c>
       <c r="Q8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="R8" t="s">
         <v>307</v>
@@ -2010,7 +2010,7 @@
         <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G9" t="s">
         <v>110</v>
@@ -2043,7 +2043,7 @@
         <v>290</v>
       </c>
       <c r="Q9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R9" t="s">
         <v>308</v>
@@ -2066,7 +2066,7 @@
         <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G10" t="s">
         <v>111</v>
@@ -2099,7 +2099,7 @@
         <v>291</v>
       </c>
       <c r="Q10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="R10" t="s">
         <v>309</v>
@@ -2122,7 +2122,7 @@
         <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G11" t="s">
         <v>112</v>
@@ -2155,7 +2155,7 @@
         <v>292</v>
       </c>
       <c r="Q11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R11" t="s">
         <v>310</v>
@@ -2178,7 +2178,7 @@
         <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G12" t="s">
         <v>113</v>
@@ -2211,7 +2211,7 @@
         <v>293</v>
       </c>
       <c r="Q12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R12" t="s">
         <v>311</v>
@@ -2234,7 +2234,7 @@
         <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G13" t="s">
         <v>114</v>
@@ -2267,7 +2267,7 @@
         <v>294</v>
       </c>
       <c r="Q13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R13" t="s">
         <v>312</v>
@@ -2290,7 +2290,7 @@
         <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G14" t="s">
         <v>115</v>
@@ -2323,7 +2323,7 @@
         <v>85</v>
       </c>
       <c r="Q14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R14" t="s">
         <v>313</v>
@@ -2379,7 +2379,7 @@
         <v>86</v>
       </c>
       <c r="Q15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R15" t="s">
         <v>101</v>
@@ -2435,7 +2435,7 @@
         <v>295</v>
       </c>
       <c r="Q16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R16" t="s">
         <v>314</v>
@@ -2458,7 +2458,7 @@
         <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="G17" t="s">
         <v>101</v>
@@ -2491,7 +2491,7 @@
         <v>88</v>
       </c>
       <c r="Q17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R17" t="s">
         <v>101</v>
@@ -2547,7 +2547,7 @@
         <v>296</v>
       </c>
       <c r="Q18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R18" t="s">
         <v>315</v>
@@ -2570,7 +2570,7 @@
         <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G19" t="s">
         <v>119</v>
@@ -2603,7 +2603,7 @@
         <v>90</v>
       </c>
       <c r="Q19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R19" t="s">
         <v>316</v>
@@ -2626,7 +2626,7 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G20" t="s">
         <v>91</v>
@@ -2659,7 +2659,7 @@
         <v>91</v>
       </c>
       <c r="Q20" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="R20" t="s">
         <v>317</v>
@@ -2682,7 +2682,7 @@
         <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G21" t="s">
         <v>120</v>
@@ -2715,7 +2715,7 @@
         <v>297</v>
       </c>
       <c r="Q21" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="R21" t="s">
         <v>318</v>
@@ -2738,7 +2738,7 @@
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -2762,7 +2762,7 @@
         <v>236</v>
       </c>
       <c r="N22" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="O22" t="s">
         <v>282</v>
@@ -2771,7 +2771,7 @@
         <v>93</v>
       </c>
       <c r="Q22" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="R22" t="s">
         <v>319</v>
@@ -2794,7 +2794,7 @@
         <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G23" t="s">
         <v>101</v>
@@ -2827,7 +2827,7 @@
         <v>94</v>
       </c>
       <c r="Q23" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="R23" t="s">
         <v>320</v>
@@ -2850,7 +2850,7 @@
         <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G24" t="s">
         <v>101</v>
@@ -2883,7 +2883,7 @@
         <v>95</v>
       </c>
       <c r="Q24" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="R24" t="s">
         <v>321</v>
@@ -2962,7 +2962,7 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G26" t="s">
         <v>101</v>
@@ -2995,7 +2995,7 @@
         <v>97</v>
       </c>
       <c r="Q26" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="R26" t="s">
         <v>322</v>
@@ -3018,7 +3018,7 @@
         <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G27" t="s">
         <v>101</v>
@@ -3042,7 +3042,7 @@
         <v>241</v>
       </c>
       <c r="N27" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="O27" t="s">
         <v>283</v>
@@ -3051,7 +3051,7 @@
         <v>298</v>
       </c>
       <c r="Q27" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="R27" t="s">
         <v>323</v>
@@ -3074,7 +3074,7 @@
         <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="G28" t="s">
         <v>101</v>
@@ -3098,7 +3098,7 @@
         <v>242</v>
       </c>
       <c r="N28" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="O28" t="s">
         <v>284</v>
@@ -3107,7 +3107,7 @@
         <v>299</v>
       </c>
       <c r="Q28" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="R28" t="s">
         <v>324</v>
@@ -3130,7 +3130,7 @@
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G29" t="s">
         <v>101</v>
@@ -3154,7 +3154,7 @@
         <v>243</v>
       </c>
       <c r="N29" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="O29" t="s">
         <v>285</v>
